--- a/artfynd/A 31764-2023 artfynd.xlsx
+++ b/artfynd/A 31764-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118103355</v>
+        <v>211166</v>
       </c>
       <c r="B2" t="n">
-        <v>84933</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92310</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1970</v>
+        <v>303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skorpdyna</t>
+          <t>Rosenporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Biscogniauxia nummularia</t>
+          <t>Ceriporia excelsa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bull.:Fr.) Kuntze</t>
+          <t>(S. Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Risens NR, Sk</t>
+          <t>Risens NR, södra delen, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398310</v>
+        <v>398273</v>
       </c>
       <c r="R2" t="n">
-        <v>6160747</v>
+        <v>6160786</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2004-03-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2004-03-30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På nedfallen bit av gren eller stam. Stroma 5-20 x 5-15 mm insjunkna i barken. Stroma &lt;1 mm tjocka.  Sp. ellipsoid, 9,2-11,8 x 5,1-6,8. Groddspringa i sporens hela längd. I dåligt skick så endast sporer funna inga sporsäckar.</t>
+          <t>På grov boklåga utmed stig.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,42 +759,392 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>bok</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Insänkt i barken</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica # Insänkt i barken</t>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Ädellövskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Bokskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Andreas Malmqvist</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Andreas Malmqvist</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>118103355</v>
+      </c>
+      <c r="B3" t="n">
+        <v>86115</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1970</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skorpdyna</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Biscogniauxia nummularia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Bull.:Fr.) Kuntze</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Risens NR, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>398310</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6160747</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Genarp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På nedfallen bit av gren eller stam. Stroma 5-20 x 5-15 mm insjunkna i barken. Stroma &lt;1 mm tjocka.  Sp. ellipsoid, 9,2-11,8 x 5,1-6,8. Groddspringa i sporens hela längd. I dåligt skick så endast sporer funna inga sporsäckar.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Insänkt i barken</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica # Insänkt i barken</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Anders Dahl</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Anders Dahl</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1098039</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92342</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sydlig sotticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ischnoderma resinosum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schrad.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Risens NR, södra delen, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>398273</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6160786</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Genarp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2004-03-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2004-03-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På grov boklåga utmed stig.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Ädellövskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Bokskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Andreas Malmqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Andreas Malmqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>62263808</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56895</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100088</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig snok</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Natrix natrix</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Risen Storkakroken, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>398397</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6160892</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Genarp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2016-05-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2016-05-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Skinnet uppfläkt och hål efter klor/tänder på annat ställe.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Peter Johnsen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Peter Johnsen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
